--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10575,6 +10575,612 @@
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128077707</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>619364</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6970783</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128077706</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>619346</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6970865</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128077709</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>619257</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6970630</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128077654</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80092</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>619295</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6970505</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128077705</v>
+      </c>
+      <c r="B91" t="n">
+        <v>88752</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>510</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>619346</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6970865</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128077708</v>
+      </c>
+      <c r="B92" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Brännan, Ång</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>619305</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6970733</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>128077707</v>
       </c>
       <c r="B87" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>128077706</v>
       </c>
       <c r="B88" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>128077709</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>128077654</v>
       </c>
       <c r="B90" t="n">
-        <v>80092</v>
+        <v>80095</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>128077708</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>128077707</v>
       </c>
       <c r="B87" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>128077706</v>
       </c>
       <c r="B88" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>128077709</v>
       </c>
       <c r="B89" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>128077654</v>
       </c>
       <c r="B90" t="n">
-        <v>80095</v>
+        <v>80148</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>128077708</v>
       </c>
       <c r="B92" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>128077707</v>
       </c>
       <c r="B87" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>128077706</v>
       </c>
       <c r="B88" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>128077709</v>
       </c>
       <c r="B89" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>128077654</v>
       </c>
       <c r="B90" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88853</v>
+        <v>88865</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>128077708</v>
       </c>
       <c r="B92" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 50984-2020 artfynd.xlsx
+++ b/artfynd/A 50984-2020 artfynd.xlsx
@@ -10580,7 +10580,7 @@
         <v>128077707</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>128077709</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>128077654</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>128077705</v>
       </c>
       <c r="B91" t="n">
-        <v>88865</v>
+        <v>88867</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>128077708</v>
       </c>
       <c r="B92" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
